--- a/data/trans_bre/P71_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 11,93</t>
+          <t>1,98; 11,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 5,77</t>
+          <t>-5,97; 5,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 5,33</t>
+          <t>-4,07; 6,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,07</t>
+          <t>-4,05; 0,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,63; 233,7</t>
+          <t>21,67; 211,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 45,97</t>
+          <t>-34,35; 47,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 54,23</t>
+          <t>-28,01; 60,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 31,76</t>
+          <t>-61,9; 25,5</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 11,72</t>
+          <t>1,52; 12,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 9,06</t>
+          <t>-1,86; 9,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 9,63</t>
+          <t>-4,04; 9,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,38</t>
+          <t>0,01; 5,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 116,52</t>
+          <t>8,71; 122,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 75,63</t>
+          <t>-13,66; 82,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 50,83</t>
+          <t>-15,6; 53,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 222,51</t>
+          <t>0,06; 241,66</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 14,18</t>
+          <t>-0,46; 14,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 2,94</t>
+          <t>-11,96; 2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 4,81</t>
+          <t>-12,63; 4,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 11,76</t>
+          <t>-2,74; 10,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 108,64</t>
+          <t>-3,75; 101,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 9,3</t>
+          <t>-33,07; 7,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 13,67</t>
+          <t>-32,58; 12,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 283,33</t>
+          <t>-24,51; 328,69</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 7,03</t>
+          <t>-1,04; 7,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 3,7</t>
+          <t>-7,1; 2,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 4,49</t>
+          <t>-4,5; 4,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 1,88</t>
+          <t>-9,93; 1,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 32,89</t>
+          <t>-4,51; 35,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 10,13</t>
+          <t>-18,11; 7,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 12,38</t>
+          <t>-10,91; 13,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 12,69</t>
+          <t>-57,98; 12,09</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 8,05</t>
+          <t>-5,4; 7,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 5,63</t>
+          <t>-5,73; 5,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 11,21</t>
+          <t>0,25; 11,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 28,68</t>
+          <t>2,25; 28,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 27,05</t>
+          <t>-14,28; 26,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 15,16</t>
+          <t>-12,73; 14,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 25,27</t>
+          <t>0,46; 25,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 127,68</t>
+          <t>7,75; 127,91</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,68; 25,14</t>
+          <t>16,53; 25,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 16,26</t>
+          <t>4,9; 16,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 16,31</t>
+          <t>3,97; 16,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 10,4</t>
+          <t>-4,2; 10,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>99,53; 290,95</t>
+          <t>106,76; 290,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,27; 98,78</t>
+          <t>19,59; 99,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,06; 90,73</t>
+          <t>12,91; 88,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 135,31</t>
+          <t>-22,74; 150,52</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,72; 11,81</t>
+          <t>7,61; 11,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,38</t>
+          <t>-1,35; 3,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,49</t>
+          <t>-0,16; 4,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,01</t>
+          <t>1,51; 10,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,36; 68,73</t>
+          <t>40,06; 69,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 11,53</t>
+          <t>-4,24; 10,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 13,83</t>
+          <t>-0,46; 14,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 101,9</t>
+          <t>11,1; 102,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P71_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-30,19%</t>
+          <t>-28,34%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,12</t>
+          <t>2,44; 12,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 5,84</t>
+          <t>-5,91; 5,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 6,21</t>
+          <t>-3,84; 5,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,77</t>
+          <t>-4,1; 0,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,67; 211,79</t>
+          <t>28,72; 231,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 47,84</t>
+          <t>-34,41; 43,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 60,17</t>
+          <t>-26,33; 54,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-61,9; 25,5</t>
+          <t>-59,51; 25,79</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 12,35</t>
+          <t>1,44; 12,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 9,26</t>
+          <t>-1,93; 9,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 9,85</t>
+          <t>-3,35; 9,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,01; 5,53</t>
+          <t>-0,03; 5,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 122,29</t>
+          <t>7,65; 118,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 82,9</t>
+          <t>-12,69; 86,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 53,43</t>
+          <t>-12,81; 49,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 241,66</t>
+          <t>-3,14; 211,98</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>-10,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 14,16</t>
+          <t>0,11; 14,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 2,25</t>
+          <t>-11,68; 2,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 4,43</t>
+          <t>-12,59; 5,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 10,96</t>
+          <t>-6,73; 3,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 101,17</t>
+          <t>0,13; 109,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 7,47</t>
+          <t>-32,29; 6,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 12,07</t>
+          <t>-31,94; 14,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 328,69</t>
+          <t>-42,19; 34,23</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,83</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-18,57%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 7,45</t>
+          <t>-0,78; 7,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 2,72</t>
+          <t>-6,89; 3,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 4,8</t>
+          <t>-4,93; 3,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 1,77</t>
+          <t>-2,23; 4,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 35,34</t>
+          <t>-3,77; 34,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 7,42</t>
+          <t>-17,23; 8,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 13,24</t>
+          <t>-12,08; 10,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,98; 12,09</t>
+          <t>-13,56; 28,48</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,28</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 7,77</t>
+          <t>-4,74; 9,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 5,76</t>
+          <t>-5,48; 6,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 11,3</t>
+          <t>-0,04; 11,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 28,25</t>
+          <t>-4,45; 5,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 26,66</t>
+          <t>-13,0; 32,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 14,68</t>
+          <t>-12,46; 16,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 25,5</t>
+          <t>-0,05; 26,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,75; 127,91</t>
+          <t>-13,68; 20,67</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,53; 25,44</t>
+          <t>16,08; 25,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,22</t>
+          <t>5,04; 16,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,97; 16,18</t>
+          <t>4,67; 16,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 10,82</t>
+          <t>-7,63; 9,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106,76; 290,86</t>
+          <t>102,99; 302,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,59; 99,3</t>
+          <t>21,15; 101,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,91; 88,11</t>
+          <t>17,48; 91,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 150,52</t>
+          <t>-30,66; 102,64</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,9</t>
+          <t>7,66; 11,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,24</t>
+          <t>-1,39; 3,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,77</t>
+          <t>-0,11; 4,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 10,99</t>
+          <t>0,82; 4,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,06; 69,62</t>
+          <t>40,53; 68,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 10,93</t>
+          <t>-4,42; 10,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 14,67</t>
+          <t>-0,31; 13,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,1; 102,97</t>
+          <t>5,09; 32,26</t>
         </is>
       </c>
     </row>
